--- a/legal_forms/011_service_fee_agreement_template--legal_forms.xlsx
+++ b/legal_forms/011_service_fee_agreement_template--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -744,7 +744,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Payment Terms</t>
+          <t>Payment Terms Terms</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Payment Method</t>
+          <t>Payment Method Terms</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -789,12 +789,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>payment_terms_terms</t>
+          <t>payment_terms_terms_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Payment Terms</t>
+          <t>Payment Terms Terms 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>payment_terms_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Payment Terms</t>
+          <t>Payment Terms 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -954,12 +954,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>payment_terms</t>
+          <t>payment_terms_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Payment Terms</t>
+          <t>Payment Terms 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
